--- a/AAII_Financials/Yearly/AMBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMBI_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
   <si>
     <t>AMBI</t>
   </si>
@@ -656,43 +656,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="F7" s="2">
-        <v>43830</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H7" s="2" t="s">
         <v>3</v>
       </c>
@@ -702,50 +702,62 @@
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>478500</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>311300</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>151900</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>67300</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>386200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>247200</v>
+      </c>
+      <c r="F9" s="3">
+        <v>114300</v>
+      </c>
+      <c r="G9" s="3">
+        <v>47300</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -756,23 +768,29 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>64100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>37600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>20000</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -783,9 +801,15 @@
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -797,8 +821,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -823,9 +849,15 @@
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -850,9 +882,15 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -877,9 +915,15 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -904,9 +948,15 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -915,22 +965,24 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1200</v>
+        <v>411900</v>
       </c>
       <c r="E17" s="3">
-        <v>300</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
+        <v>249100</v>
+      </c>
+      <c r="F17" s="3">
+        <v>119000</v>
+      </c>
+      <c r="G17" s="3">
+        <v>50700</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -941,23 +993,29 @@
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>66600</v>
       </c>
       <c r="E18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
+        <v>62200</v>
+      </c>
+      <c r="F18" s="3">
+        <v>32900</v>
+      </c>
+      <c r="G18" s="3">
+        <v>16600</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -968,9 +1026,15 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -982,22 +1046,24 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-17900</v>
       </c>
       <c r="E20" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
+        <v>-12500</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-200</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1008,77 +1074,95 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>82500</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>70600</v>
       </c>
       <c r="F21" s="3">
-        <v>0</v>
+        <v>45400</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+        <v>20600</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>28500</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+        <v>1100</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>9400</v>
+        <v>20100</v>
       </c>
       <c r="E23" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
+        <v>43000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>32500</v>
+      </c>
+      <c r="G23" s="3">
+        <v>15300</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1089,36 +1173,48 @@
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+        <v>3100</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1143,23 +1239,29 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>9400</v>
+        <v>3200</v>
       </c>
       <c r="E26" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
+        <v>34700</v>
+      </c>
+      <c r="F26" s="3">
+        <v>25500</v>
+      </c>
+      <c r="G26" s="3">
+        <v>12200</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1170,23 +1272,29 @@
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>9400</v>
+        <v>-11500</v>
       </c>
       <c r="E27" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
+        <v>29800</v>
+      </c>
+      <c r="F27" s="3">
+        <v>24200</v>
+      </c>
+      <c r="G27" s="3">
+        <v>11400</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1197,9 +1305,15 @@
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1224,9 +1338,15 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1251,9 +1371,15 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1278,9 +1404,15 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1305,23 +1437,29 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>17900</v>
       </c>
       <c r="E32" s="3">
-        <v>8400</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
+        <v>12500</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="G32" s="3">
+        <v>200</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1332,23 +1470,29 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>9400</v>
+        <v>-11500</v>
       </c>
       <c r="E33" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
+        <v>29800</v>
+      </c>
+      <c r="F33" s="3">
+        <v>24200</v>
+      </c>
+      <c r="G33" s="3">
+        <v>11400</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1359,9 +1503,15 @@
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1386,23 +1536,29 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>9400</v>
+        <v>-11500</v>
       </c>
       <c r="E35" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
+        <v>29800</v>
+      </c>
+      <c r="F35" s="3">
+        <v>24200</v>
+      </c>
+      <c r="G35" s="3">
+        <v>11400</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1413,29 +1569,35 @@
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="F38" s="2">
-        <v>43830</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1445,9 +1607,15 @@
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1459,8 +1627,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1472,22 +1642,24 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>500</v>
+        <v>78200</v>
       </c>
       <c r="E41" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
+        <v>50200</v>
+      </c>
+      <c r="F41" s="3">
+        <v>22000</v>
+      </c>
+      <c r="G41" s="3">
+        <v>11400</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1498,9 +1670,15 @@
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1525,77 +1703,95 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>162900</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>136600</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>46700</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+        <v>22900</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>18700</v>
       </c>
       <c r="E45" s="3">
-        <v>300</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
+        <v>19200</v>
+      </c>
+      <c r="F45" s="3">
+        <v>13500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>7900</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1606,23 +1802,29 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>600</v>
+        <v>266100</v>
       </c>
       <c r="E46" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
+        <v>209300</v>
+      </c>
+      <c r="F46" s="3">
+        <v>83800</v>
+      </c>
+      <c r="G46" s="3">
+        <v>43200</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1633,23 +1835,29 @@
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>253000</v>
+        <v>7000</v>
       </c>
       <c r="E47" s="3">
-        <v>253000</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+        <v>9000</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G47" s="3">
+        <v>900</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -1660,63 +1868,81 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>161900</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
+        <v>108000</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>61300</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+        <v>19000</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>350300</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>297900</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+        <v>41500</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1741,9 +1967,15 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1768,36 +2000,48 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>9700</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+        <v>6400</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1822,23 +2066,29 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>253700</v>
+        <v>796200</v>
       </c>
       <c r="E54" s="3">
-        <v>254400</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
+        <v>633900</v>
+      </c>
+      <c r="F54" s="3">
+        <v>264400</v>
+      </c>
+      <c r="G54" s="3">
+        <v>111000</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -1849,9 +2099,15 @@
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1863,8 +2119,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1876,22 +2134,24 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>600</v>
+        <v>34100</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
+        <v>27100</v>
+      </c>
+      <c r="F57" s="3">
+        <v>7300</v>
+      </c>
+      <c r="G57" s="3">
+        <v>3700</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -1902,50 +2162,62 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>34500</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>30700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+        <v>3400</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>200</v>
+        <v>79800</v>
       </c>
       <c r="E59" s="3">
-        <v>200</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
+        <v>74700</v>
+      </c>
+      <c r="F59" s="3">
+        <v>43600</v>
+      </c>
+      <c r="G59" s="3">
+        <v>11900</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -1956,23 +2228,29 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>700</v>
+        <v>148400</v>
       </c>
       <c r="E60" s="3">
-        <v>300</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
+        <v>132500</v>
+      </c>
+      <c r="F60" s="3">
+        <v>64000</v>
+      </c>
+      <c r="G60" s="3">
+        <v>19000</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -1983,23 +2261,29 @@
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>321400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>363700</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>110600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>21900</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2010,23 +2294,29 @@
       <c r="J61" s="3">
         <v>0</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>19400</v>
+        <v>75800</v>
       </c>
       <c r="E62" s="3">
-        <v>29900</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
+        <v>55100</v>
+      </c>
+      <c r="F62" s="3">
+        <v>27400</v>
+      </c>
+      <c r="G62" s="3">
+        <v>9600</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2037,9 +2327,15 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2064,9 +2360,15 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2091,9 +2393,15 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2118,23 +2426,29 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>20100</v>
+        <v>597900</v>
       </c>
       <c r="E66" s="3">
-        <v>30200</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
+        <v>566400</v>
+      </c>
+      <c r="F66" s="3">
+        <v>204200</v>
+      </c>
+      <c r="G66" s="3">
+        <v>54900</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2145,9 +2459,15 @@
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2159,8 +2479,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2185,9 +2507,15 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2212,9 +2540,15 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2239,9 +2573,15 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2266,23 +2606,29 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-19500</v>
+        <v>-11500</v>
       </c>
       <c r="E72" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
+        <v>55900</v>
+      </c>
+      <c r="F72" s="3">
+        <v>32500</v>
+      </c>
+      <c r="G72" s="3">
+        <v>14100</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2293,9 +2639,15 @@
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2320,9 +2672,15 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2347,9 +2705,15 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2374,23 +2738,29 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>233600</v>
+        <v>198300</v>
       </c>
       <c r="E76" s="3">
-        <v>224200</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
+        <v>67500</v>
+      </c>
+      <c r="F76" s="3">
+        <v>60200</v>
+      </c>
+      <c r="G76" s="3">
+        <v>56100</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2401,9 +2771,15 @@
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2428,29 +2804,35 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="F80" s="2">
-        <v>43830</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2460,23 +2842,29 @@
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>9400</v>
+        <v>-11500</v>
       </c>
       <c r="E81" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
+        <v>29800</v>
+      </c>
+      <c r="F81" s="3">
+        <v>24200</v>
+      </c>
+      <c r="G81" s="3">
+        <v>11400</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2487,9 +2875,15 @@
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2501,35 +2895,43 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>33600</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>20700</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>11100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+        <v>4200</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2554,9 +2956,15 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2581,9 +2989,15 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2608,9 +3022,15 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2635,9 +3055,15 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2662,23 +3088,29 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-600</v>
+        <v>14500</v>
       </c>
       <c r="E89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
+        <v>87000</v>
+      </c>
+      <c r="F89" s="3">
+        <v>11900</v>
+      </c>
+      <c r="G89" s="3">
+        <v>6000</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -2689,9 +3121,15 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2703,35 +3141,43 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-44400</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-17700</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-22900</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+        <v>-4100</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2756,9 +3202,15 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2783,23 +3235,29 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-76100</v>
       </c>
       <c r="E94" s="3">
-        <v>-253000</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+        <v>-244000</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-82900</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-21700</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -2810,9 +3268,15 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2824,8 +3288,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -2850,9 +3316,15 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2877,9 +3349,15 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2904,9 +3382,15 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2931,23 +3415,29 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100100</v>
       </c>
       <c r="E100" s="3">
-        <v>254600</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
+        <v>183800</v>
+      </c>
+      <c r="F100" s="3">
+        <v>80000</v>
+      </c>
+      <c r="G100" s="3">
+        <v>20100</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -2958,50 +3448,62 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-10500</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+        <v>4800</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-600</v>
+        <v>28000</v>
       </c>
       <c r="E102" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
+        <v>28200</v>
+      </c>
+      <c r="F102" s="3">
+        <v>10600</v>
+      </c>
+      <c r="G102" s="3">
+        <v>9100</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
@@ -3012,7 +3514,13 @@
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AMBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMBI_YR_FIN.xlsx
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>478500</v>
+        <v>465500</v>
       </c>
       <c r="E8" s="3">
-        <v>311300</v>
+        <v>302800</v>
       </c>
       <c r="F8" s="3">
-        <v>151900</v>
+        <v>147800</v>
       </c>
       <c r="G8" s="3">
-        <v>67300</v>
+        <v>65500</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -748,16 +748,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>386200</v>
+        <v>375700</v>
       </c>
       <c r="E9" s="3">
-        <v>247200</v>
+        <v>240400</v>
       </c>
       <c r="F9" s="3">
-        <v>114300</v>
+        <v>111200</v>
       </c>
       <c r="G9" s="3">
-        <v>47300</v>
+        <v>46000</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -781,16 +781,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>92300</v>
+        <v>89800</v>
       </c>
       <c r="E10" s="3">
-        <v>64100</v>
+        <v>62400</v>
       </c>
       <c r="F10" s="3">
-        <v>37600</v>
+        <v>36600</v>
       </c>
       <c r="G10" s="3">
-        <v>20000</v>
+        <v>19400</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -973,16 +973,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>411900</v>
+        <v>400700</v>
       </c>
       <c r="E17" s="3">
-        <v>249100</v>
+        <v>242300</v>
       </c>
       <c r="F17" s="3">
-        <v>119000</v>
+        <v>115800</v>
       </c>
       <c r="G17" s="3">
-        <v>50700</v>
+        <v>49300</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -1006,16 +1006,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>66600</v>
+        <v>64800</v>
       </c>
       <c r="E18" s="3">
-        <v>62200</v>
+        <v>60500</v>
       </c>
       <c r="F18" s="3">
-        <v>32900</v>
+        <v>32000</v>
       </c>
       <c r="G18" s="3">
-        <v>16600</v>
+        <v>16200</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1054,10 +1054,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-17900</v>
+        <v>-17500</v>
       </c>
       <c r="E20" s="3">
-        <v>-12500</v>
+        <v>-12200</v>
       </c>
       <c r="F20" s="3">
         <v>1300</v>
@@ -1087,16 +1087,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>82500</v>
+        <v>79600</v>
       </c>
       <c r="E21" s="3">
-        <v>70600</v>
+        <v>68300</v>
       </c>
       <c r="F21" s="3">
-        <v>45400</v>
+        <v>44000</v>
       </c>
       <c r="G21" s="3">
-        <v>20600</v>
+        <v>19900</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1120,16 +1120,16 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>28500</v>
+        <v>27700</v>
       </c>
       <c r="E22" s="3">
-        <v>6700</v>
+        <v>6500</v>
       </c>
       <c r="F22" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="G22" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1153,16 +1153,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>20100</v>
+        <v>19600</v>
       </c>
       <c r="E23" s="3">
-        <v>43000</v>
+        <v>41800</v>
       </c>
       <c r="F23" s="3">
-        <v>32500</v>
+        <v>31600</v>
       </c>
       <c r="G23" s="3">
-        <v>15300</v>
+        <v>14900</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1186,16 +1186,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>17000</v>
+        <v>16500</v>
       </c>
       <c r="E24" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="F24" s="3">
-        <v>7000</v>
+        <v>6800</v>
       </c>
       <c r="G24" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1252,16 +1252,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="E26" s="3">
-        <v>34700</v>
+        <v>33800</v>
       </c>
       <c r="F26" s="3">
-        <v>25500</v>
+        <v>24800</v>
       </c>
       <c r="G26" s="3">
-        <v>12200</v>
+        <v>11900</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1285,16 +1285,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-11500</v>
+        <v>-11200</v>
       </c>
       <c r="E27" s="3">
-        <v>29800</v>
+        <v>29000</v>
       </c>
       <c r="F27" s="3">
-        <v>24200</v>
+        <v>23600</v>
       </c>
       <c r="G27" s="3">
-        <v>11400</v>
+        <v>11100</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1450,10 +1450,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>17900</v>
+        <v>17500</v>
       </c>
       <c r="E32" s="3">
-        <v>12500</v>
+        <v>12200</v>
       </c>
       <c r="F32" s="3">
         <v>-1300</v>
@@ -1483,16 +1483,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-11500</v>
+        <v>-11200</v>
       </c>
       <c r="E33" s="3">
-        <v>29800</v>
+        <v>29000</v>
       </c>
       <c r="F33" s="3">
-        <v>24200</v>
+        <v>23600</v>
       </c>
       <c r="G33" s="3">
-        <v>11400</v>
+        <v>11100</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1549,16 +1549,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-11500</v>
+        <v>-11200</v>
       </c>
       <c r="E35" s="3">
-        <v>29800</v>
+        <v>29000</v>
       </c>
       <c r="F35" s="3">
-        <v>24200</v>
+        <v>23600</v>
       </c>
       <c r="G35" s="3">
-        <v>11400</v>
+        <v>11100</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1650,16 +1650,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>78200</v>
+        <v>76100</v>
       </c>
       <c r="E41" s="3">
-        <v>50200</v>
+        <v>48800</v>
       </c>
       <c r="F41" s="3">
-        <v>22000</v>
+        <v>21400</v>
       </c>
       <c r="G41" s="3">
-        <v>11400</v>
+        <v>11100</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1716,16 +1716,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>162900</v>
+        <v>158500</v>
       </c>
       <c r="E43" s="3">
-        <v>136600</v>
+        <v>132800</v>
       </c>
       <c r="F43" s="3">
-        <v>46700</v>
+        <v>45400</v>
       </c>
       <c r="G43" s="3">
-        <v>22900</v>
+        <v>22300</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1749,7 +1749,7 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6300</v>
+        <v>6100</v>
       </c>
       <c r="E44" s="3">
         <v>3300</v>
@@ -1758,7 +1758,7 @@
         <v>1600</v>
       </c>
       <c r="G44" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1782,16 +1782,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E45" s="3">
         <v>18700</v>
       </c>
-      <c r="E45" s="3">
-        <v>19200</v>
-      </c>
       <c r="F45" s="3">
-        <v>13500</v>
+        <v>13200</v>
       </c>
       <c r="G45" s="3">
-        <v>7900</v>
+        <v>7700</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1815,16 +1815,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>266100</v>
+        <v>258900</v>
       </c>
       <c r="E46" s="3">
-        <v>209300</v>
+        <v>203600</v>
       </c>
       <c r="F46" s="3">
-        <v>83800</v>
+        <v>81500</v>
       </c>
       <c r="G46" s="3">
-        <v>43200</v>
+        <v>42000</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1848,13 +1848,13 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>7000</v>
+        <v>6800</v>
       </c>
       <c r="E47" s="3">
-        <v>9000</v>
+        <v>8700</v>
       </c>
       <c r="F47" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="G47" s="3">
         <v>900</v>
@@ -1881,16 +1881,16 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>161900</v>
+        <v>157500</v>
       </c>
       <c r="E48" s="3">
-        <v>108000</v>
+        <v>105000</v>
       </c>
       <c r="F48" s="3">
-        <v>61300</v>
+        <v>59600</v>
       </c>
       <c r="G48" s="3">
-        <v>19000</v>
+        <v>18500</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1914,16 +1914,16 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>350300</v>
+        <v>340700</v>
       </c>
       <c r="E49" s="3">
-        <v>297900</v>
+        <v>289800</v>
       </c>
       <c r="F49" s="3">
-        <v>110000</v>
+        <v>107000</v>
       </c>
       <c r="G49" s="3">
-        <v>41500</v>
+        <v>40400</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -2013,16 +2013,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10900</v>
+        <v>10600</v>
       </c>
       <c r="E52" s="3">
-        <v>9700</v>
+        <v>9400</v>
       </c>
       <c r="F52" s="3">
-        <v>8100</v>
+        <v>7900</v>
       </c>
       <c r="G52" s="3">
-        <v>6400</v>
+        <v>6200</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -2079,16 +2079,16 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>796200</v>
+        <v>774500</v>
       </c>
       <c r="E54" s="3">
-        <v>633900</v>
+        <v>616600</v>
       </c>
       <c r="F54" s="3">
-        <v>264400</v>
+        <v>257200</v>
       </c>
       <c r="G54" s="3">
-        <v>111000</v>
+        <v>108000</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -2142,16 +2142,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>34100</v>
+        <v>33200</v>
       </c>
       <c r="E57" s="3">
-        <v>27100</v>
+        <v>26400</v>
       </c>
       <c r="F57" s="3">
-        <v>7300</v>
+        <v>7100</v>
       </c>
       <c r="G57" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -2175,16 +2175,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>34500</v>
+        <v>33500</v>
       </c>
       <c r="E58" s="3">
-        <v>30700</v>
+        <v>29900</v>
       </c>
       <c r="F58" s="3">
-        <v>13000</v>
+        <v>12700</v>
       </c>
       <c r="G58" s="3">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -2208,16 +2208,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>79800</v>
+        <v>77600</v>
       </c>
       <c r="E59" s="3">
-        <v>74700</v>
+        <v>72600</v>
       </c>
       <c r="F59" s="3">
-        <v>43600</v>
+        <v>42400</v>
       </c>
       <c r="G59" s="3">
-        <v>11900</v>
+        <v>11600</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2241,16 +2241,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>148400</v>
+        <v>144300</v>
       </c>
       <c r="E60" s="3">
-        <v>132500</v>
+        <v>128900</v>
       </c>
       <c r="F60" s="3">
-        <v>64000</v>
+        <v>62200</v>
       </c>
       <c r="G60" s="3">
-        <v>19000</v>
+        <v>18500</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -2274,16 +2274,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>321400</v>
+        <v>312600</v>
       </c>
       <c r="E61" s="3">
-        <v>363700</v>
+        <v>353800</v>
       </c>
       <c r="F61" s="3">
-        <v>110600</v>
+        <v>107600</v>
       </c>
       <c r="G61" s="3">
-        <v>21900</v>
+        <v>21300</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2307,16 +2307,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>75800</v>
+        <v>73700</v>
       </c>
       <c r="E62" s="3">
-        <v>55100</v>
+        <v>53600</v>
       </c>
       <c r="F62" s="3">
-        <v>27400</v>
+        <v>26600</v>
       </c>
       <c r="G62" s="3">
-        <v>9600</v>
+        <v>9400</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2439,16 +2439,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>597900</v>
+        <v>581600</v>
       </c>
       <c r="E66" s="3">
-        <v>566400</v>
+        <v>550900</v>
       </c>
       <c r="F66" s="3">
-        <v>204200</v>
+        <v>198600</v>
       </c>
       <c r="G66" s="3">
-        <v>54900</v>
+        <v>53400</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2619,16 +2619,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-11500</v>
+        <v>-11200</v>
       </c>
       <c r="E72" s="3">
-        <v>55900</v>
+        <v>54400</v>
       </c>
       <c r="F72" s="3">
-        <v>32500</v>
+        <v>31700</v>
       </c>
       <c r="G72" s="3">
-        <v>14100</v>
+        <v>13700</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2751,16 +2751,16 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>198300</v>
+        <v>192900</v>
       </c>
       <c r="E76" s="3">
-        <v>67500</v>
+        <v>65700</v>
       </c>
       <c r="F76" s="3">
-        <v>60200</v>
+        <v>58600</v>
       </c>
       <c r="G76" s="3">
-        <v>56100</v>
+        <v>54600</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2855,16 +2855,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-11500</v>
+        <v>-11200</v>
       </c>
       <c r="E81" s="3">
-        <v>29800</v>
+        <v>29000</v>
       </c>
       <c r="F81" s="3">
-        <v>24200</v>
+        <v>23600</v>
       </c>
       <c r="G81" s="3">
-        <v>11400</v>
+        <v>11100</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2903,16 +2903,16 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>33600</v>
+        <v>32700</v>
       </c>
       <c r="E83" s="3">
-        <v>20700</v>
+        <v>20100</v>
       </c>
       <c r="F83" s="3">
-        <v>11100</v>
+        <v>10800</v>
       </c>
       <c r="G83" s="3">
-        <v>4200</v>
+        <v>4000</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -3101,16 +3101,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>14500</v>
+        <v>14100</v>
       </c>
       <c r="E89" s="3">
-        <v>87000</v>
+        <v>84600</v>
       </c>
       <c r="F89" s="3">
-        <v>11900</v>
+        <v>11600</v>
       </c>
       <c r="G89" s="3">
-        <v>6000</v>
+        <v>5800</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -3149,16 +3149,16 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-44400</v>
+        <v>-43200</v>
       </c>
       <c r="E91" s="3">
-        <v>-17700</v>
+        <v>-17200</v>
       </c>
       <c r="F91" s="3">
-        <v>-22900</v>
+        <v>-22200</v>
       </c>
       <c r="G91" s="3">
-        <v>-4100</v>
+        <v>-4000</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -3248,16 +3248,16 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-76100</v>
+        <v>-74000</v>
       </c>
       <c r="E94" s="3">
-        <v>-244000</v>
+        <v>-237400</v>
       </c>
       <c r="F94" s="3">
-        <v>-82900</v>
+        <v>-80600</v>
       </c>
       <c r="G94" s="3">
-        <v>-21700</v>
+        <v>-21100</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3428,16 +3428,16 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>100100</v>
+        <v>97400</v>
       </c>
       <c r="E100" s="3">
-        <v>183800</v>
+        <v>178800</v>
       </c>
       <c r="F100" s="3">
-        <v>80000</v>
+        <v>77900</v>
       </c>
       <c r="G100" s="3">
-        <v>20100</v>
+        <v>19600</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -3461,16 +3461,16 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-10500</v>
+        <v>-10200</v>
       </c>
       <c r="E101" s="3">
         <v>1400</v>
       </c>
       <c r="F101" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="G101" s="3">
-        <v>4800</v>
+        <v>4600</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -3494,16 +3494,16 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>28000</v>
+        <v>27300</v>
       </c>
       <c r="E102" s="3">
-        <v>28200</v>
+        <v>27400</v>
       </c>
       <c r="F102" s="3">
-        <v>10600</v>
+        <v>10300</v>
       </c>
       <c r="G102" s="3">
-        <v>9100</v>
+        <v>8900</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/AMBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMBI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
   <si>
     <t>AMBI</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -693,14 +693,14 @@
       <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="H7" s="2">
+        <v>43100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>42735</v>
+      </c>
+      <c r="J7" s="2">
+        <v>42369</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -715,25 +715,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>465500</v>
+        <v>533800</v>
       </c>
       <c r="E8" s="3">
-        <v>302800</v>
+        <v>318700</v>
       </c>
       <c r="F8" s="3">
-        <v>147800</v>
+        <v>147600</v>
       </c>
       <c r="G8" s="3">
-        <v>65500</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>70100</v>
+      </c>
+      <c r="H8" s="3">
+        <v>32100</v>
+      </c>
+      <c r="I8" s="3">
+        <v>28200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>21600</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -748,25 +748,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>375700</v>
+        <v>430800</v>
       </c>
       <c r="E9" s="3">
-        <v>240400</v>
+        <v>253000</v>
       </c>
       <c r="F9" s="3">
-        <v>111200</v>
+        <v>111000</v>
       </c>
       <c r="G9" s="3">
-        <v>46000</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>49300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>18300</v>
+      </c>
+      <c r="I9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>9900</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -781,25 +781,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>89800</v>
+        <v>102900</v>
       </c>
       <c r="E10" s="3">
-        <v>62400</v>
+        <v>65700</v>
       </c>
       <c r="F10" s="3">
-        <v>36600</v>
+        <v>36500</v>
       </c>
       <c r="G10" s="3">
-        <v>19400</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>20800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>13900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>13100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>11700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -894,26 +894,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -928,25 +928,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>15200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -973,25 +973,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>400700</v>
+        <v>459500</v>
       </c>
       <c r="E17" s="3">
-        <v>242300</v>
+        <v>255700</v>
       </c>
       <c r="F17" s="3">
-        <v>115800</v>
+        <v>115600</v>
       </c>
       <c r="G17" s="3">
-        <v>49300</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>52800</v>
+      </c>
+      <c r="H17" s="3">
+        <v>26100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>22200</v>
+      </c>
+      <c r="J17" s="3">
+        <v>14900</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1006,25 +1006,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>64800</v>
+        <v>74300</v>
       </c>
       <c r="E18" s="3">
-        <v>60500</v>
+        <v>63000</v>
       </c>
       <c r="F18" s="3">
         <v>32000</v>
       </c>
       <c r="G18" s="3">
-        <v>16200</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>17300</v>
+      </c>
+      <c r="H18" s="3">
+        <v>6100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>6700</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1054,25 +1054,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-17500</v>
+        <v>21400</v>
       </c>
       <c r="E20" s="3">
-        <v>-12200</v>
+        <v>2700</v>
       </c>
       <c r="F20" s="3">
-        <v>1300</v>
+        <v>-600</v>
       </c>
       <c r="G20" s="3">
+        <v>300</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1087,25 +1087,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>79600</v>
+        <v>76500</v>
       </c>
       <c r="E21" s="3">
-        <v>68300</v>
+        <v>75500</v>
       </c>
       <c r="F21" s="3">
-        <v>44000</v>
+        <v>43400</v>
       </c>
       <c r="G21" s="3">
-        <v>19900</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>21100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>7200</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -1120,25 +1120,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>27700</v>
+        <v>33500</v>
       </c>
       <c r="E22" s="3">
-        <v>6500</v>
+        <v>17600</v>
       </c>
       <c r="F22" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="G22" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>1200</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I22" s="3">
+        <v>700</v>
+      </c>
+      <c r="J22" s="3">
+        <v>300</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1153,25 +1153,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>19600</v>
+        <v>22500</v>
       </c>
       <c r="E23" s="3">
-        <v>41800</v>
+        <v>44000</v>
       </c>
       <c r="F23" s="3">
         <v>31600</v>
       </c>
       <c r="G23" s="3">
-        <v>14900</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>15900</v>
+      </c>
+      <c r="H23" s="3">
+        <v>6400</v>
+      </c>
+      <c r="I23" s="3">
+        <v>7200</v>
+      </c>
+      <c r="J23" s="3">
+        <v>6600</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1186,25 +1186,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>16500</v>
+        <v>18900</v>
       </c>
       <c r="E24" s="3">
-        <v>8100</v>
+        <v>8500</v>
       </c>
       <c r="F24" s="3">
         <v>6800</v>
       </c>
       <c r="G24" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+        <v>3200</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2200</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1252,25 +1252,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>3100</v>
+        <v>3500</v>
       </c>
       <c r="E26" s="3">
-        <v>33800</v>
+        <v>35500</v>
       </c>
       <c r="F26" s="3">
         <v>24800</v>
       </c>
       <c r="G26" s="3">
-        <v>11900</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>12700</v>
+      </c>
+      <c r="H26" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>4400</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1285,25 +1285,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-11200</v>
+        <v>-12900</v>
       </c>
       <c r="E27" s="3">
-        <v>29000</v>
+        <v>30600</v>
       </c>
       <c r="F27" s="3">
-        <v>23600</v>
+        <v>23500</v>
       </c>
       <c r="G27" s="3">
-        <v>11100</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>11900</v>
+      </c>
+      <c r="H27" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I27" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J27" s="3">
+        <v>4400</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1450,25 +1450,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>17500</v>
+        <v>-21400</v>
       </c>
       <c r="E32" s="3">
-        <v>12200</v>
+        <v>-2700</v>
       </c>
       <c r="F32" s="3">
-        <v>-1300</v>
+        <v>600</v>
       </c>
       <c r="G32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1483,25 +1483,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-11200</v>
+        <v>-12900</v>
       </c>
       <c r="E33" s="3">
-        <v>29000</v>
+        <v>30500</v>
       </c>
       <c r="F33" s="3">
-        <v>23600</v>
+        <v>23500</v>
       </c>
       <c r="G33" s="3">
-        <v>11100</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>11900</v>
+      </c>
+      <c r="H33" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I33" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>4400</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1549,25 +1549,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-11200</v>
+        <v>-12900</v>
       </c>
       <c r="E35" s="3">
-        <v>29000</v>
+        <v>30500</v>
       </c>
       <c r="F35" s="3">
-        <v>23600</v>
+        <v>23500</v>
       </c>
       <c r="G35" s="3">
-        <v>11100</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>11900</v>
+      </c>
+      <c r="H35" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I35" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>4400</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1598,14 +1598,14 @@
       <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="H38" s="2">
+        <v>43100</v>
+      </c>
+      <c r="I38" s="2">
+        <v>42735</v>
+      </c>
+      <c r="J38" s="2">
+        <v>42369</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1650,25 +1650,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>76100</v>
+        <v>87200</v>
       </c>
       <c r="E41" s="3">
-        <v>48800</v>
+        <v>51400</v>
       </c>
       <c r="F41" s="3">
-        <v>21400</v>
+        <v>21300</v>
       </c>
       <c r="G41" s="3">
-        <v>11100</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>11900</v>
+      </c>
+      <c r="H41" s="3">
+        <v>300</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J41" s="3">
+        <v>700</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1716,25 +1716,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>158500</v>
+        <v>191100</v>
       </c>
       <c r="E43" s="3">
-        <v>132800</v>
+        <v>146700</v>
       </c>
       <c r="F43" s="3">
-        <v>45400</v>
+        <v>46600</v>
       </c>
       <c r="G43" s="3">
-        <v>22300</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>22000</v>
+      </c>
+      <c r="H43" s="3">
+        <v>9600</v>
+      </c>
+      <c r="I43" s="3">
+        <v>7100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>4500</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -1749,25 +1749,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6100</v>
+        <v>7000</v>
       </c>
       <c r="E44" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="F44" s="3">
         <v>1600</v>
       </c>
       <c r="G44" s="3">
-        <v>900</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>1000</v>
+      </c>
+      <c r="H44" s="3">
+        <v>200</v>
+      </c>
+      <c r="I44" s="3">
+        <v>300</v>
+      </c>
+      <c r="J44" s="3">
+        <v>100</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1782,16 +1782,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>18200</v>
+        <v>4800</v>
       </c>
       <c r="E45" s="3">
-        <v>18700</v>
+        <v>5600</v>
       </c>
       <c r="F45" s="3">
-        <v>13200</v>
+        <v>11600</v>
       </c>
       <c r="G45" s="3">
-        <v>7700</v>
+        <v>10000</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1815,25 +1815,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>258900</v>
+        <v>296800</v>
       </c>
       <c r="E46" s="3">
-        <v>203600</v>
+        <v>214300</v>
       </c>
       <c r="F46" s="3">
-        <v>81500</v>
+        <v>81400</v>
       </c>
       <c r="G46" s="3">
-        <v>42000</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>45000</v>
+      </c>
+      <c r="H46" s="3">
+        <v>10100</v>
+      </c>
+      <c r="I46" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J46" s="3">
+        <v>5300</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1847,26 +1847,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>6800</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3">
-        <v>8700</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>900</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>1400</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1000</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1881,25 +1881,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>157500</v>
+        <v>180600</v>
       </c>
       <c r="E48" s="3">
-        <v>105000</v>
+        <v>110500</v>
       </c>
       <c r="F48" s="3">
-        <v>59600</v>
+        <v>59500</v>
       </c>
       <c r="G48" s="3">
-        <v>18500</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>20000</v>
+      </c>
+      <c r="H48" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1800</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -1914,25 +1914,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>340700</v>
+        <v>390700</v>
       </c>
       <c r="E49" s="3">
-        <v>289800</v>
+        <v>305000</v>
       </c>
       <c r="F49" s="3">
-        <v>107000</v>
+        <v>106900</v>
       </c>
       <c r="G49" s="3">
-        <v>40400</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>43100</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2013,25 +2013,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10600</v>
+        <v>7300</v>
       </c>
       <c r="E52" s="3">
-        <v>9400</v>
+        <v>7900</v>
       </c>
       <c r="F52" s="3">
-        <v>7900</v>
+        <v>7500</v>
       </c>
       <c r="G52" s="3">
-        <v>6200</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>1100</v>
+      </c>
+      <c r="H52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I52" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>800</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2079,25 +2079,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>774500</v>
+        <v>888100</v>
       </c>
       <c r="E54" s="3">
-        <v>616600</v>
+        <v>649000</v>
       </c>
       <c r="F54" s="3">
-        <v>257200</v>
+        <v>256800</v>
       </c>
       <c r="G54" s="3">
-        <v>108000</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>115700</v>
+      </c>
+      <c r="H54" s="3">
+        <v>21100</v>
+      </c>
+      <c r="I54" s="3">
+        <v>19400</v>
+      </c>
+      <c r="J54" s="3">
+        <v>8900</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2142,25 +2142,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>33200</v>
+        <v>38000</v>
       </c>
       <c r="E57" s="3">
-        <v>26400</v>
+        <v>27700</v>
       </c>
       <c r="F57" s="3">
         <v>7100</v>
       </c>
       <c r="G57" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>3900</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J57" s="3">
+        <v>600</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2175,25 +2175,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>33500</v>
+        <v>38500</v>
       </c>
       <c r="E58" s="3">
-        <v>29900</v>
+        <v>31400</v>
       </c>
       <c r="F58" s="3">
-        <v>12700</v>
+        <v>12600</v>
       </c>
       <c r="G58" s="3">
-        <v>3300</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>3500</v>
+      </c>
+      <c r="H58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>300</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2208,25 +2208,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>77600</v>
+        <v>60100</v>
       </c>
       <c r="E59" s="3">
-        <v>72600</v>
+        <v>47800</v>
       </c>
       <c r="F59" s="3">
-        <v>42400</v>
+        <v>35400</v>
       </c>
       <c r="G59" s="3">
-        <v>11600</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>7400</v>
+      </c>
+      <c r="H59" s="3">
+        <v>300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>100</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2241,25 +2241,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>144300</v>
+        <v>165500</v>
       </c>
       <c r="E60" s="3">
-        <v>128900</v>
+        <v>135600</v>
       </c>
       <c r="F60" s="3">
-        <v>62200</v>
+        <v>62100</v>
       </c>
       <c r="G60" s="3">
-        <v>18500</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>19800</v>
+      </c>
+      <c r="H60" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I60" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J60" s="3">
+        <v>2500</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2274,25 +2274,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>312600</v>
+        <v>358500</v>
       </c>
       <c r="E61" s="3">
-        <v>353800</v>
+        <v>372400</v>
       </c>
       <c r="F61" s="3">
-        <v>107600</v>
+        <v>20900</v>
       </c>
       <c r="G61" s="3">
-        <v>21300</v>
+        <v>22800</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2307,25 +2307,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>73700</v>
+        <v>45800</v>
       </c>
       <c r="E62" s="3">
-        <v>53600</v>
+        <v>20300</v>
       </c>
       <c r="F62" s="3">
-        <v>26600</v>
+        <v>107200</v>
       </c>
       <c r="G62" s="3">
-        <v>9400</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>7500</v>
+      </c>
+      <c r="H62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J62" s="3">
+        <v>700</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2439,25 +2439,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>581600</v>
+        <v>608400</v>
       </c>
       <c r="E66" s="3">
-        <v>550900</v>
+        <v>564400</v>
       </c>
       <c r="F66" s="3">
-        <v>198600</v>
+        <v>196200</v>
       </c>
       <c r="G66" s="3">
-        <v>53400</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>52700</v>
+      </c>
+      <c r="H66" s="3">
+        <v>10600</v>
+      </c>
+      <c r="I66" s="3">
+        <v>10600</v>
+      </c>
+      <c r="J66" s="3">
+        <v>3600</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2619,25 +2619,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-11200</v>
+        <v>-12900</v>
       </c>
       <c r="E72" s="3">
-        <v>54400</v>
+        <v>57300</v>
       </c>
       <c r="F72" s="3">
-        <v>31700</v>
+        <v>31600</v>
       </c>
       <c r="G72" s="3">
-        <v>13700</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>14700</v>
+      </c>
+      <c r="H72" s="3">
+        <v>8100</v>
+      </c>
+      <c r="I72" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J72" s="3">
+        <v>3400</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2751,25 +2751,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>192900</v>
+        <v>221100</v>
       </c>
       <c r="E76" s="3">
-        <v>65700</v>
+        <v>69100</v>
       </c>
       <c r="F76" s="3">
-        <v>58600</v>
+        <v>58500</v>
       </c>
       <c r="G76" s="3">
-        <v>54600</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>58500</v>
+      </c>
+      <c r="H76" s="3">
+        <v>10600</v>
+      </c>
+      <c r="I76" s="3">
+        <v>8800</v>
+      </c>
+      <c r="J76" s="3">
+        <v>5300</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2833,14 +2833,14 @@
       <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="H80" s="2">
+        <v>43100</v>
+      </c>
+      <c r="I80" s="2">
+        <v>42735</v>
+      </c>
+      <c r="J80" s="2">
+        <v>42369</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2855,25 +2855,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-11200</v>
+        <v>-12900</v>
       </c>
       <c r="E81" s="3">
-        <v>29000</v>
+        <v>30500</v>
       </c>
       <c r="F81" s="3">
-        <v>23600</v>
+        <v>23500</v>
       </c>
       <c r="G81" s="3">
-        <v>11100</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>11900</v>
+      </c>
+      <c r="H81" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I81" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>4400</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2903,25 +2903,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>32700</v>
+        <v>35800</v>
       </c>
       <c r="E83" s="3">
-        <v>20100</v>
+        <v>21000</v>
       </c>
       <c r="F83" s="3">
         <v>10800</v>
       </c>
       <c r="G83" s="3">
-        <v>4000</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>4300</v>
+      </c>
+      <c r="H83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I83" s="3">
+        <v>400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3101,25 +3101,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>14100</v>
+        <v>16200</v>
       </c>
       <c r="E89" s="3">
-        <v>84600</v>
+        <v>89100</v>
       </c>
       <c r="F89" s="3">
-        <v>11600</v>
+        <v>11500</v>
       </c>
       <c r="G89" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>6300</v>
+      </c>
+      <c r="H89" s="3">
+        <v>4700</v>
+      </c>
+      <c r="I89" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>4600</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3149,25 +3149,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-43200</v>
+        <v>-49500</v>
       </c>
       <c r="E91" s="3">
-        <v>-17200</v>
+        <v>-18100</v>
       </c>
       <c r="F91" s="3">
         <v>-22200</v>
       </c>
       <c r="G91" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+        <v>-4200</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-400</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3248,25 +3248,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-74000</v>
+        <v>-84900</v>
       </c>
       <c r="E94" s="3">
-        <v>-237400</v>
+        <v>-249800</v>
       </c>
       <c r="F94" s="3">
-        <v>-80600</v>
+        <v>-80500</v>
       </c>
       <c r="G94" s="3">
-        <v>-21100</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-22700</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1000</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3296,7 +3296,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -3428,25 +3428,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>97400</v>
+        <v>111700</v>
       </c>
       <c r="E100" s="3">
-        <v>178800</v>
+        <v>188200</v>
       </c>
       <c r="F100" s="3">
-        <v>77900</v>
+        <v>77800</v>
       </c>
       <c r="G100" s="3">
-        <v>19600</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>21000</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="I100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-3500</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3461,16 +3461,16 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-10200</v>
+        <v>-11700</v>
       </c>
       <c r="E101" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="F101" s="3">
         <v>1400</v>
       </c>
       <c r="G101" s="3">
-        <v>4600</v>
+        <v>5000</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -3494,25 +3494,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>27300</v>
+        <v>31300</v>
       </c>
       <c r="E102" s="3">
-        <v>27400</v>
+        <v>28900</v>
       </c>
       <c r="F102" s="3">
         <v>10300</v>
       </c>
       <c r="G102" s="3">
-        <v>8900</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>9500</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I102" s="3">
+        <v>200</v>
+      </c>
+      <c r="J102" s="3">
+        <v>200</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/AMBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMBI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>AMBI</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -693,14 +693,14 @@
       <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
-        <v>43100</v>
-      </c>
-      <c r="I7" s="2">
-        <v>42735</v>
-      </c>
-      <c r="J7" s="2">
-        <v>42369</v>
+      <c r="H7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -726,14 +726,14 @@
       <c r="G8" s="3">
         <v>70100</v>
       </c>
-      <c r="H8" s="3">
-        <v>32100</v>
-      </c>
-      <c r="I8" s="3">
-        <v>28200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>21600</v>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -759,14 +759,14 @@
       <c r="G9" s="3">
         <v>49300</v>
       </c>
-      <c r="H9" s="3">
-        <v>18300</v>
-      </c>
-      <c r="I9" s="3">
-        <v>15100</v>
-      </c>
-      <c r="J9" s="3">
-        <v>9900</v>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -792,14 +792,14 @@
       <c r="G10" s="3">
         <v>20800</v>
       </c>
-      <c r="H10" s="3">
-        <v>13900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>13100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>11700</v>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -940,13 +940,13 @@
         <v>4000</v>
       </c>
       <c r="H15" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -984,14 +984,14 @@
       <c r="G17" s="3">
         <v>52800</v>
       </c>
-      <c r="H17" s="3">
-        <v>26100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>22200</v>
-      </c>
-      <c r="J17" s="3">
-        <v>14900</v>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1017,14 +1017,14 @@
       <c r="G18" s="3">
         <v>17300</v>
       </c>
-      <c r="H18" s="3">
-        <v>6100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>6700</v>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1065,14 +1065,14 @@
       <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-200</v>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1099,13 +1099,13 @@
         <v>21100</v>
       </c>
       <c r="H21" s="3">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -1131,14 +1131,14 @@
       <c r="G22" s="3">
         <v>1200</v>
       </c>
-      <c r="H22" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>700</v>
-      </c>
-      <c r="J22" s="3">
-        <v>300</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1164,14 +1164,14 @@
       <c r="G23" s="3">
         <v>15900</v>
       </c>
-      <c r="H23" s="3">
-        <v>6400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>7200</v>
-      </c>
-      <c r="J23" s="3">
-        <v>6600</v>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1197,14 +1197,14 @@
       <c r="G24" s="3">
         <v>3200</v>
       </c>
-      <c r="H24" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>2200</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1263,14 +1263,14 @@
       <c r="G26" s="3">
         <v>12700</v>
       </c>
-      <c r="H26" s="3">
-        <v>4600</v>
-      </c>
-      <c r="I26" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J26" s="3">
-        <v>4400</v>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1296,14 +1296,14 @@
       <c r="G27" s="3">
         <v>11900</v>
       </c>
-      <c r="H27" s="3">
-        <v>4600</v>
-      </c>
-      <c r="I27" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>4400</v>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1461,14 +1461,14 @@
       <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>200</v>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1494,14 +1494,14 @@
       <c r="G33" s="3">
         <v>11900</v>
       </c>
-      <c r="H33" s="3">
-        <v>4600</v>
-      </c>
-      <c r="I33" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J33" s="3">
-        <v>4400</v>
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1560,14 +1560,14 @@
       <c r="G35" s="3">
         <v>11900</v>
       </c>
-      <c r="H35" s="3">
-        <v>4600</v>
-      </c>
-      <c r="I35" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J35" s="3">
-        <v>4400</v>
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1598,14 +1598,14 @@
       <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
-        <v>43100</v>
-      </c>
-      <c r="I38" s="2">
-        <v>42735</v>
-      </c>
-      <c r="J38" s="2">
-        <v>42369</v>
+      <c r="H38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1661,14 +1661,14 @@
       <c r="G41" s="3">
         <v>11900</v>
       </c>
-      <c r="H41" s="3">
-        <v>300</v>
-      </c>
-      <c r="I41" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>700</v>
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1727,14 +1727,14 @@
       <c r="G43" s="3">
         <v>22000</v>
       </c>
-      <c r="H43" s="3">
-        <v>9600</v>
-      </c>
-      <c r="I43" s="3">
-        <v>7100</v>
-      </c>
-      <c r="J43" s="3">
-        <v>4500</v>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -1760,14 +1760,14 @@
       <c r="G44" s="3">
         <v>1000</v>
       </c>
-      <c r="H44" s="3">
-        <v>200</v>
-      </c>
-      <c r="I44" s="3">
-        <v>300</v>
-      </c>
-      <c r="J44" s="3">
-        <v>100</v>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1826,14 +1826,14 @@
       <c r="G46" s="3">
         <v>45000</v>
       </c>
-      <c r="H46" s="3">
-        <v>10100</v>
-      </c>
-      <c r="I46" s="3">
-        <v>8400</v>
-      </c>
-      <c r="J46" s="3">
-        <v>5300</v>
+      <c r="H46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1859,14 +1859,14 @@
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I47" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J47" s="3">
-        <v>1000</v>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1892,14 +1892,14 @@
       <c r="G48" s="3">
         <v>20000</v>
       </c>
-      <c r="H48" s="3">
-        <v>4100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>4600</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1800</v>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -1925,14 +1925,14 @@
       <c r="G49" s="3">
         <v>43100</v>
       </c>
-      <c r="H49" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2024,14 +2024,14 @@
       <c r="G52" s="3">
         <v>1100</v>
       </c>
-      <c r="H52" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J52" s="3">
-        <v>800</v>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2090,14 +2090,14 @@
       <c r="G54" s="3">
         <v>115700</v>
       </c>
-      <c r="H54" s="3">
-        <v>21100</v>
-      </c>
-      <c r="I54" s="3">
-        <v>19400</v>
-      </c>
-      <c r="J54" s="3">
-        <v>8900</v>
+      <c r="H54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2153,14 +2153,14 @@
       <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J57" s="3">
-        <v>600</v>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2186,14 +2186,14 @@
       <c r="G58" s="3">
         <v>3500</v>
       </c>
-      <c r="H58" s="3">
-        <v>2400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>300</v>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2219,14 +2219,14 @@
       <c r="G59" s="3">
         <v>7400</v>
       </c>
-      <c r="H59" s="3">
-        <v>300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2252,14 +2252,14 @@
       <c r="G60" s="3">
         <v>19800</v>
       </c>
-      <c r="H60" s="3">
-        <v>7000</v>
-      </c>
-      <c r="I60" s="3">
-        <v>6200</v>
-      </c>
-      <c r="J60" s="3">
-        <v>2500</v>
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2286,13 +2286,13 @@
         <v>22800</v>
       </c>
       <c r="H61" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2318,14 +2318,14 @@
       <c r="G62" s="3">
         <v>7500</v>
       </c>
-      <c r="H62" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>700</v>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2450,14 +2450,14 @@
       <c r="G66" s="3">
         <v>52700</v>
       </c>
-      <c r="H66" s="3">
-        <v>10600</v>
-      </c>
-      <c r="I66" s="3">
-        <v>10600</v>
-      </c>
-      <c r="J66" s="3">
-        <v>3600</v>
+      <c r="H66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2630,14 +2630,14 @@
       <c r="G72" s="3">
         <v>14700</v>
       </c>
-      <c r="H72" s="3">
-        <v>8100</v>
-      </c>
-      <c r="I72" s="3">
-        <v>6700</v>
-      </c>
-      <c r="J72" s="3">
-        <v>3400</v>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2762,14 +2762,14 @@
       <c r="G76" s="3">
         <v>58500</v>
       </c>
-      <c r="H76" s="3">
-        <v>10600</v>
-      </c>
-      <c r="I76" s="3">
-        <v>8800</v>
-      </c>
-      <c r="J76" s="3">
-        <v>5300</v>
+      <c r="H76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2833,14 +2833,14 @@
       <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
-        <v>43100</v>
-      </c>
-      <c r="I80" s="2">
-        <v>42735</v>
-      </c>
-      <c r="J80" s="2">
-        <v>42369</v>
+      <c r="H80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2866,14 +2866,14 @@
       <c r="G81" s="3">
         <v>11900</v>
       </c>
-      <c r="H81" s="3">
-        <v>4600</v>
-      </c>
-      <c r="I81" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J81" s="3">
-        <v>4400</v>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2914,14 +2914,14 @@
       <c r="G83" s="3">
         <v>4300</v>
       </c>
-      <c r="H83" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>300</v>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       <c r="G89" s="3">
         <v>6300</v>
       </c>
-      <c r="H89" s="3">
-        <v>4700</v>
-      </c>
-      <c r="I89" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J89" s="3">
-        <v>4600</v>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3160,14 +3160,14 @@
       <c r="G91" s="3">
         <v>-4200</v>
       </c>
-      <c r="H91" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-400</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3259,14 +3259,14 @@
       <c r="G94" s="3">
         <v>-22700</v>
       </c>
-      <c r="H94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-1000</v>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3439,14 +3439,14 @@
       <c r="G100" s="3">
         <v>21000</v>
       </c>
-      <c r="H100" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="I100" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-3500</v>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3506,13 +3506,13 @@
         <v>9500</v>
       </c>
       <c r="H102" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/AMBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMBI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
   <si>
     <t>AMBI</t>
   </si>
@@ -656,46 +656,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
       </c>
@@ -708,60 +708,66 @@
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>532500</v>
+      </c>
+      <c r="E8" s="3">
         <v>533800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>318700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>147600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>70100</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>430800</v>
+        <v>452800</v>
       </c>
       <c r="E9" s="3">
+        <v>428800</v>
+      </c>
+      <c r="F9" s="3">
         <v>253000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>111000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>49300</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -774,27 +780,30 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>102900</v>
+        <v>79700</v>
       </c>
       <c r="E10" s="3">
+        <v>105000</v>
+      </c>
+      <c r="F10" s="3">
         <v>65700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>36500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20800</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -807,9 +816,12 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +835,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -855,9 +868,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,9 +904,12 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -915,33 +934,36 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E15" s="3">
         <v>23600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>15200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4000</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
@@ -954,9 +976,12 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,26 +992,27 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>459500</v>
+        <v>452200</v>
       </c>
       <c r="E17" s="3">
+        <v>434100</v>
+      </c>
+      <c r="F17" s="3">
         <v>255700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>115600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>52800</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
       </c>
@@ -999,27 +1025,30 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>74300</v>
+        <v>80300</v>
       </c>
       <c r="E18" s="3">
+        <v>99700</v>
+      </c>
+      <c r="F18" s="3">
         <v>63000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>32000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>17300</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1032,9 +1061,12 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,26 +1080,27 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>21400</v>
+        <v>18300</v>
       </c>
       <c r="E20" s="3">
+        <v>24700</v>
+      </c>
+      <c r="F20" s="3">
         <v>2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,27 +1113,30 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>76500</v>
+        <v>88700</v>
       </c>
       <c r="E21" s="3">
+        <v>98600</v>
+      </c>
+      <c r="F21" s="3">
         <v>75500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>43400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>21100</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
       <c r="I21" s="3">
         <v>0</v>
       </c>
@@ -1113,60 +1149,66 @@
       <c r="L21" s="3">
         <v>0</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E22" s="3">
         <v>33500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1200</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>22500</v>
+        <v>23500</v>
       </c>
       <c r="E23" s="3">
+        <v>43600</v>
+      </c>
+      <c r="F23" s="3">
         <v>44000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>31600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>15900</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1179,42 +1221,48 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E24" s="3">
         <v>18900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3200</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,27 +1293,30 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>3500</v>
+        <v>12500</v>
       </c>
       <c r="E26" s="3">
+        <v>24700</v>
+      </c>
+      <c r="F26" s="3">
         <v>35500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>24800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12700</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1278,27 +1329,30 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-12900</v>
+        <v>-300</v>
       </c>
       <c r="E27" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F27" s="3">
         <v>30600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>23500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11900</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1311,9 +1365,12 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1437,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,27 +1509,30 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-21400</v>
+        <v>-18300</v>
       </c>
       <c r="E32" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1476,27 +1545,30 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-12900</v>
+        <v>-300</v>
       </c>
       <c r="E33" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F33" s="3">
         <v>30500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>23500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11900</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1509,9 +1581,12 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,27 +1617,30 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-12900</v>
+        <v>-300</v>
       </c>
       <c r="E35" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F35" s="3">
         <v>30500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>23500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11900</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1575,32 +1653,35 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1613,9 +1694,12 @@
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,26 +1729,27 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>87200</v>
+        <v>58100</v>
       </c>
       <c r="E41" s="3">
+        <v>86200</v>
+      </c>
+      <c r="F41" s="3">
         <v>51400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11900</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1676,9 +1762,12 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1709,93 +1798,102 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>203000</v>
+      </c>
+      <c r="E43" s="3">
         <v>191100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>146700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>46600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>22000</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E44" s="3">
         <v>7000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1000</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E45" s="3">
         <v>4800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,27 +1906,30 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>296800</v>
+        <v>283000</v>
       </c>
       <c r="E46" s="3">
+        <v>295800</v>
+      </c>
+      <c r="F46" s="3">
         <v>214300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>81400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>45000</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1841,21 +1942,24 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
         <v>1400</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1874,75 +1978,84 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>210400</v>
+      </c>
+      <c r="E48" s="3">
         <v>180600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>110500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>59500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>362700</v>
+      </c>
+      <c r="E49" s="3">
         <v>390700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>305000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>106900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>43100</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,42 +2122,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E52" s="3">
         <v>7300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,27 +2194,30 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>888100</v>
+        <v>933300</v>
       </c>
       <c r="E54" s="3">
+        <v>899400</v>
+      </c>
+      <c r="F54" s="3">
         <v>649000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>256800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>115700</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2105,9 +2230,12 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,26 +2265,27 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>38000</v>
+        <v>35300</v>
       </c>
       <c r="E57" s="3">
+        <v>32900</v>
+      </c>
+      <c r="F57" s="3">
         <v>27700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2168,60 +2298,66 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>61700</v>
+      </c>
+      <c r="E58" s="3">
         <v>38500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>31400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3500</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>60100</v>
+        <v>31200</v>
       </c>
       <c r="E59" s="3">
+        <v>63100</v>
+      </c>
+      <c r="F59" s="3">
         <v>47800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>35400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7400</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,27 +2370,30 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>165500</v>
+        <v>154800</v>
       </c>
       <c r="E60" s="3">
+        <v>163200</v>
+      </c>
+      <c r="F60" s="3">
         <v>135600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>62100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19800</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2267,27 +2406,30 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>358500</v>
+        <v>493900</v>
       </c>
       <c r="E61" s="3">
+        <v>434000</v>
+      </c>
+      <c r="F61" s="3">
         <v>372400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>20900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>22800</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2300,27 +2442,30 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>45800</v>
+        <v>5100</v>
       </c>
       <c r="E62" s="3">
+        <v>39500</v>
+      </c>
+      <c r="F62" s="3">
         <v>20300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>107200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7500</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,9 +2478,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,27 +2586,30 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>608400</v>
+        <v>692800</v>
       </c>
       <c r="E66" s="3">
+        <v>675400</v>
+      </c>
+      <c r="F66" s="3">
         <v>564400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>196200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>52700</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2465,9 +2622,12 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,27 +2782,30 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-12900</v>
+        <v>55300</v>
       </c>
       <c r="E72" s="3">
+        <v>70800</v>
+      </c>
+      <c r="F72" s="3">
         <v>57300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>31600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14700</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,9 +2818,12 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,26 +2926,29 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>221100</v>
+        <v>181200</v>
       </c>
       <c r="E76" s="3">
+        <v>165500</v>
+      </c>
+      <c r="F76" s="3">
         <v>69100</v>
-      </c>
-      <c r="F76" s="3">
-        <v>58500</v>
       </c>
       <c r="G76" s="3">
         <v>58500</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
+      <c r="H76" s="3">
+        <v>58500</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2777,9 +2962,12 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,32 +2998,35 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2848,27 +3039,30 @@
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-12900</v>
+        <v>-300</v>
       </c>
       <c r="E81" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F81" s="3">
         <v>30500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>23500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11900</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2881,9 +3075,12 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,41 +3094,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E83" s="3">
         <v>35800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4300</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,27 +3307,30 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>16200</v>
+        <v>69100</v>
       </c>
       <c r="E89" s="3">
+        <v>23100</v>
+      </c>
+      <c r="F89" s="3">
         <v>89100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6300</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3127,9 +3343,12 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,41 +3362,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-49500</v>
+        <v>-9200</v>
       </c>
       <c r="E91" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-18100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-22200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4200</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,27 +3467,30 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-84900</v>
+        <v>-13200</v>
       </c>
       <c r="E94" s="3">
+        <v>-54900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-249800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-80500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-22700</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,9 +3503,12 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,16 +3522,17 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>6600</v>
+        <v>8100</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3322,9 +3555,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,27 +3663,30 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>111700</v>
+        <v>-78700</v>
       </c>
       <c r="E100" s="3">
+        <v>59900</v>
+      </c>
+      <c r="F100" s="3">
         <v>188200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>77800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>21000</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3454,73 +3699,82 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-11700</v>
+        <v>13300</v>
       </c>
       <c r="E101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F101" s="3">
         <v>1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5000</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>31300</v>
+        <v>-9600</v>
       </c>
       <c r="E102" s="3">
+        <v>30300</v>
+      </c>
+      <c r="F102" s="3">
         <v>28900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9500</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AMBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMBI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>AMBI</t>
   </si>
@@ -718,7 +718,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>532500</v>
+        <v>525200</v>
       </c>
       <c r="E8" s="3">
         <v>533800</v>
@@ -754,10 +754,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>452800</v>
+        <v>447800</v>
       </c>
       <c r="E9" s="3">
-        <v>428800</v>
+        <v>430800</v>
       </c>
       <c r="F9" s="3">
         <v>253000</v>
@@ -790,10 +790,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>79700</v>
+        <v>77400</v>
       </c>
       <c r="E10" s="3">
-        <v>105000</v>
+        <v>102900</v>
       </c>
       <c r="F10" s="3">
         <v>65700</v>
@@ -953,10 +953,10 @@
         <v>26700</v>
       </c>
       <c r="E15" s="3">
-        <v>23600</v>
+        <v>25300</v>
       </c>
       <c r="F15" s="3">
-        <v>15200</v>
+        <v>21200</v>
       </c>
       <c r="G15" s="3">
         <v>10800</v>
@@ -999,10 +999,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>452200</v>
+        <v>446700</v>
       </c>
       <c r="E17" s="3">
-        <v>434100</v>
+        <v>459500</v>
       </c>
       <c r="F17" s="3">
         <v>255700</v>
@@ -1035,10 +1035,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>80300</v>
+        <v>78500</v>
       </c>
       <c r="E18" s="3">
-        <v>99700</v>
+        <v>74300</v>
       </c>
       <c r="F18" s="3">
         <v>63000</v>
@@ -1087,13 +1087,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>18300</v>
+        <v>18500</v>
       </c>
       <c r="E20" s="3">
-        <v>24700</v>
+        <v>21400</v>
       </c>
       <c r="F20" s="3">
-        <v>2700</v>
+        <v>19000</v>
       </c>
       <c r="G20" s="3">
         <v>-600</v>
@@ -1123,13 +1123,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>88700</v>
+        <v>86700</v>
       </c>
       <c r="E21" s="3">
-        <v>98600</v>
+        <v>78200</v>
       </c>
       <c r="F21" s="3">
-        <v>75500</v>
+        <v>65200</v>
       </c>
       <c r="G21" s="3">
         <v>43400</v>
@@ -1159,13 +1159,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>40700</v>
+        <v>41700</v>
       </c>
       <c r="E22" s="3">
         <v>33500</v>
       </c>
-      <c r="F22" s="3">
-        <v>17600</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <v>1800</v>
@@ -1195,10 +1195,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>23500</v>
+        <v>20500</v>
       </c>
       <c r="E23" s="3">
-        <v>43600</v>
+        <v>22500</v>
       </c>
       <c r="F23" s="3">
         <v>44000</v>
@@ -1303,10 +1303,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>12500</v>
+        <v>9500</v>
       </c>
       <c r="E26" s="3">
-        <v>24700</v>
+        <v>3500</v>
       </c>
       <c r="F26" s="3">
         <v>35500</v>
@@ -1339,10 +1339,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-300</v>
+        <v>-3300</v>
       </c>
       <c r="E27" s="3">
-        <v>11000</v>
+        <v>-12900</v>
       </c>
       <c r="F27" s="3">
         <v>30600</v>
@@ -1519,13 +1519,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-18300</v>
+        <v>-18500</v>
       </c>
       <c r="E32" s="3">
-        <v>-24700</v>
+        <v>-21400</v>
       </c>
       <c r="F32" s="3">
-        <v>-2700</v>
+        <v>-19000</v>
       </c>
       <c r="G32" s="3">
         <v>600</v>
@@ -1555,10 +1555,10 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-300</v>
+        <v>-3300</v>
       </c>
       <c r="E33" s="3">
-        <v>11000</v>
+        <v>-12900</v>
       </c>
       <c r="F33" s="3">
         <v>30500</v>
@@ -1627,10 +1627,10 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-300</v>
+        <v>-3300</v>
       </c>
       <c r="E35" s="3">
-        <v>11000</v>
+        <v>-12900</v>
       </c>
       <c r="F35" s="3">
         <v>30500</v>
@@ -1736,10 +1736,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>58100</v>
+        <v>58000</v>
       </c>
       <c r="E41" s="3">
-        <v>86200</v>
+        <v>87200</v>
       </c>
       <c r="F41" s="3">
         <v>51400</v>
@@ -1916,10 +1916,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>283000</v>
+        <v>282900</v>
       </c>
       <c r="E46" s="3">
-        <v>295800</v>
+        <v>296800</v>
       </c>
       <c r="F46" s="3">
         <v>214300</v>
@@ -1988,7 +1988,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>210400</v>
+        <v>214400</v>
       </c>
       <c r="E48" s="3">
         <v>180600</v>
@@ -2132,7 +2132,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8500</v>
+        <v>9100</v>
       </c>
       <c r="E52" s="3">
         <v>7300</v>
@@ -2204,10 +2204,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>933300</v>
+        <v>937800</v>
       </c>
       <c r="E54" s="3">
-        <v>899400</v>
+        <v>888100</v>
       </c>
       <c r="F54" s="3">
         <v>649000</v>
@@ -2275,7 +2275,7 @@
         <v>35300</v>
       </c>
       <c r="E57" s="3">
-        <v>32900</v>
+        <v>38000</v>
       </c>
       <c r="F57" s="3">
         <v>27700</v>
@@ -2308,7 +2308,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>61700</v>
+        <v>66700</v>
       </c>
       <c r="E58" s="3">
         <v>38500</v>
@@ -2344,10 +2344,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>31200</v>
+        <v>29300</v>
       </c>
       <c r="E59" s="3">
-        <v>63100</v>
+        <v>60100</v>
       </c>
       <c r="F59" s="3">
         <v>47800</v>
@@ -2380,10 +2380,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>154800</v>
+        <v>158200</v>
       </c>
       <c r="E60" s="3">
-        <v>163200</v>
+        <v>165500</v>
       </c>
       <c r="F60" s="3">
         <v>135600</v>
@@ -2416,10 +2416,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>493900</v>
+        <v>436100</v>
       </c>
       <c r="E61" s="3">
-        <v>434000</v>
+        <v>358500</v>
       </c>
       <c r="F61" s="3">
         <v>372400</v>
@@ -2452,10 +2452,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5100</v>
+        <v>10800</v>
       </c>
       <c r="E62" s="3">
-        <v>39500</v>
+        <v>45800</v>
       </c>
       <c r="F62" s="3">
         <v>20300</v>
@@ -2596,10 +2596,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>692800</v>
+        <v>644100</v>
       </c>
       <c r="E66" s="3">
-        <v>675400</v>
+        <v>608400</v>
       </c>
       <c r="F66" s="3">
         <v>564400</v>
@@ -2792,10 +2792,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>55300</v>
+        <v>-13400</v>
       </c>
       <c r="E72" s="3">
-        <v>70800</v>
+        <v>-12900</v>
       </c>
       <c r="F72" s="3">
         <v>57300</v>
@@ -2936,10 +2936,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>181200</v>
+        <v>234400</v>
       </c>
       <c r="E76" s="3">
-        <v>165500</v>
+        <v>221100</v>
       </c>
       <c r="F76" s="3">
         <v>69100</v>
@@ -3049,10 +3049,10 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-300</v>
+        <v>-3300</v>
       </c>
       <c r="E81" s="3">
-        <v>11000</v>
+        <v>-12900</v>
       </c>
       <c r="F81" s="3">
         <v>30500</v>
@@ -3104,10 +3104,10 @@
         <v>50600</v>
       </c>
       <c r="E83" s="3">
-        <v>35800</v>
+        <v>37500</v>
       </c>
       <c r="F83" s="3">
-        <v>21000</v>
+        <v>21200</v>
       </c>
       <c r="G83" s="3">
         <v>10800</v>
@@ -3317,10 +3317,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>69100</v>
+        <v>68100</v>
       </c>
       <c r="E89" s="3">
-        <v>23100</v>
+        <v>16200</v>
       </c>
       <c r="F89" s="3">
         <v>89100</v>
@@ -3369,13 +3369,13 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-9200</v>
+        <v>-21800</v>
       </c>
       <c r="E91" s="3">
-        <v>-44400</v>
+        <v>-49500</v>
       </c>
       <c r="F91" s="3">
-        <v>-18100</v>
+        <v>-43600</v>
       </c>
       <c r="G91" s="3">
         <v>-22200</v>
@@ -3477,10 +3477,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-13200</v>
+        <v>-21800</v>
       </c>
       <c r="E94" s="3">
-        <v>-54900</v>
+        <v>-59200</v>
       </c>
       <c r="F94" s="3">
         <v>-249800</v>
@@ -3529,10 +3529,10 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>8100</v>
+        <v>8400</v>
       </c>
       <c r="E96" s="3">
-        <v>4000</v>
+        <v>6600</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3673,10 +3673,10 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-78700</v>
+        <v>-83100</v>
       </c>
       <c r="E100" s="3">
-        <v>59900</v>
+        <v>86000</v>
       </c>
       <c r="F100" s="3">
         <v>188200</v>
@@ -3709,10 +3709,10 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>13300</v>
+        <v>26300</v>
       </c>
       <c r="E101" s="3">
-        <v>2200</v>
+        <v>-11700</v>
       </c>
       <c r="F101" s="3">
         <v>1500</v>
@@ -3745,10 +3745,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-9600</v>
+        <v>-10500</v>
       </c>
       <c r="E102" s="3">
-        <v>30300</v>
+        <v>31300</v>
       </c>
       <c r="F102" s="3">
         <v>28900</v>
